--- a/data_extactor/batch_10_fa/batch_0088_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0088_fa.xlsx
@@ -503,12 +503,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AABACH Graphic Systems DIGRA | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe LifeCycle Production Print ES3 | Adobe PageMaker | Adobe Photoshop | Corel CorelDraw Graphics Suite | Electronics for Imaging EFI Monarch | Electronics for Imaging EFI Pace | نرم‌افزار ایمیل | Enfocus PitStop Pro | نرم‌افزار گرافیکی | نرم‌افزار ویرایش تصویر | نرم‌افزار ردیابی موجودی | نرم‌افزار زمان‌بندی کار | نرم‌افزار ردیابی کار | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Printers Software Inc. Presidio | نرم‌افزار سیستم مدیریت چاپ | QuarkXPress | نرم‌افزار SAP | کاردک چاپ (اسکوئیجی) | Xerox FreeFlow Print Server | Xerox ProfitQuick</t>
+          <t>AABACH Graphic Systems DIGRA | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe LifeCycle Production Print ES3 | Adobe PageMaker | Adobe Photoshop | Corel CorelDraw Graphics Suite | Electronics for Imaging EFI Monarch | Electronics for Imaging EFI Pace | نرم‌افزار ایمیل | Enfocus PitStop Pro | نرم‌افزار گرافیکی | نرم‌افزار ویرایش تصویر | نرم‌افزار ردیابی موجودی | نرم‌افزار زمان‌بندی کار | نرم‌افزار ردیابی کار | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Printers Software Inc. Presidio | نرم‌افزار سیستم مدیریت چاپ | QuarkXPress | نرم‌افزار SAP | تی شیشه‌شوی | Xerox FreeFlow Print Server | Xerox ProfitQuick</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>پایش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | حساسیت به مشکل | ثبات بازو-دست | زبردستی دستی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | زبردستی انگشتان | توجه انتخابی | تجسم فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | تشخیص رنگ بصری | بینایی دور | قدرت ایستا</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | مهارت انگشتان | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | تشخیص رنگ بصری | بینایی دور | قدرت ایستا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>محیط سرپوشیده، کنترل‌شده از نظر دما | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض شرایط خطرناک</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | حکاکان و تیزاب‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | کارکنان فرآیندهای عکاسی و اپراتورهای ماشین‌های پردازش تصویر | تکنسین‌ها و کارکنان پیش از چاپ | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | حکاکان و تیزاب‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به جز رایانه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | تکنسین‌ها و کارگران پیش از چاپ | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | پایش | سخن گفتن</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مدیریت و سازماندهی | تولید و فرآوری | مکانیک | خدمات مشتریان و پرسنل</t>
+          <t>مدیریت و اداره | تولید و فرآوری | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | زبردستی انگشتان | حساسیت به مشکل | بیان شفاهی | درک شفاهی | زبردستی دستی | ثبات بازو-دست | استدلال قیاسی | تجسم فضایی | وضوح گفتار | تشخیص گفتار | قدرت تنه | دقت کنترل | توجه انتخابی | استدلال استقرایی | درک کتبی | هماهنگی چند عضو | ترتیب‌دهی اطلاعات</t>
+          <t>بینایی نزدیک | مهارت انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | تجسم | وضوح گفتار | تشخیص گفتار | قدرت تنه | دقت کنترل | توجه انتخابی | استدلال استقرایی | درک کتبی | هماهنگی چند عضو | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط سرپوشیده، کنترل‌شده از نظر دما | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران</t>
+          <t>صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | الگو سازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد مرتبط | اپراتورهای ماشین چاپ | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سیم‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد مرتبط | اپراتورهای ماشین چاپ | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | بینایی نزدیک | دقت کنترل | زبردستی دستی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | دقت کنترل | مهارت دستی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارگران | صرف زمان برای انجام حرکات تکراری | سرعت تعیین‌شده توسط سرعت تجهیزات | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج کارگران دیگر | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | محیط سرپوشیده، کنترل‌شده از نظر دما</t>
+          <t>صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | سرعت تعیین‌شده توسط سرعت تجهیزات | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | برش‌دهندگان و پرداخت‌کاران دستی | ظرف‌شویان | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پولیش دستی | دستیاران--کارگران تولید | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران و جابجا‌کنندگان دستی بار، موجودی و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و تمیزکنندگان خانه‌داری | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکنی | بسته‌بندها و عدل‌بندهای دستی | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | اتوکاران منسوجات، پوشاک و مواد مرتبط | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌دهندگان و پرداخت‌کاران دستی | ظرف‌شوی‌ها | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | کمک‌کاران--کارگران تولید | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و تمیزکنندگان خانه‌داری | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | کارگران نقاشی، پوشش‌دهی و تزیین | اتوکاران منسوجات، پوشاک و مواد مرتبط | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>زبردستی دستی | ثبات بازو-دست | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | زبردستی انگشتان | قدرت تنه | زمان عکس‌العمل</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | مهارت انگشتان | قدرت تنه | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | صرف زمان برای انجام حرکات تکراری</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پولیش دستی | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکنی | بسته‌بندها و عدل‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاست | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>پایش</t>
+          <t>نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | خدمات مشتریان و پرسنل</t>
+          <t>تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | زبردستی دستی | دقت کنترل | بینایی نزدیک | زبردستی انگشتان | کنترل سرعت | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | زمان عکس‌العمل | تجسم فضایی | استدلال قیاسی | حساسیت به مشکل</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | بینایی نزدیک | مهارت انگشتان | کنترل نرخ | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | زمان عکس‌العمل | تجسم | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت نشسته | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | فشار زمانی | محیط سرپوشیده، کنترل‌شده از نظر دما | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سیم‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات بازو-دست | زبردستی انگشتان | حساسیت به مشکل | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | زبردستی دستی | توجه انتخابی | تجسم فضایی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | مهارت دستی | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | محیط سرپوشیده، کنترل‌شده از نظر دما | صرف زمان به صورت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | گفتگوهای تلفنی | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | مکالمات تلفنی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | حکاکان و تیزاب‌کاران | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پولیش دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تکنسین‌های پروتز و وسایل پزشکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگو سازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | مونتاژکنندگان و تنظیم‌کنندگان ابزارهای زمان‌سنجی | تایر سازان | رویه‌کوبان مبل</t>
+          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | حکاکان و تیزاب‌کاران | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تکنسین‌های تجهیزات پزشکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تایر سازان | روکوبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار ردیابی موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار کنترل تولید</t>
+          <t>Adobe Acrobat | نرم‌افزار ردیابی موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Production control software</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | پایش</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و سازماندهی</t>
+          <t>تولید و فرآوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات بازو-دست | دقت کنترل | زبردستی انگشتان | زبردستی دستی | سرعت ادراکی | حساسیت به مشکل | بیان شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دامنه حرکت</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | محیط سرپوشیده، کنترل‌شده از نظر دما | سرعت تعیین‌شده توسط سرعت تجهیزات | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | سرعت تعیین‌شده توسط سرعت تجهیزات | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد مرتبط | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | دوزندگان دستی | اپراتورهای چرخ خیاطی | کارگران و تعمیرکاران کفش و چرم | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سیم‌پیچی، تابندگی و کشش منسوجات | تیزکنندگان و پرداخت‌کاران ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد مرتبط | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | دوزندگان دستی | اپراتورهای چرخ خیاطی | کارگران و تعمیرکاران کفش و چرم | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | مدیریت و سازماندهی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات بازو-دست | بینایی نزدیک | دقت کنترل | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | هماهنگی چند عضو</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | طراحان الگوهای پارچه و پوشاک | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پولیش دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارکنان خشک‌شویی و لباس‌شویی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگو سازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | سازندگان و جفت‌کنندگان سازه‌های فلزی | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی منسوجات | رویه‌کوبان مبل</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | الگوسازان پارچه و پوشاک | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارکنان خشک‌شویی و لباس‌شویی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | سازندگان و مونتاژکاران فلزات سازه‌ای | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | روکوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -969,22 +969,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | زبان انگلیسی | تولید و فرآوری | مدیریت و سازماندهی | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | ثبات بازو-دست | زبردستی انگشتان | بینایی نزدیک | درک شفاهی | دقت کنترل | زبردستی دستی | ترتیب‌دهی اطلاعات | ابتکار عمل | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>تجسم | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | درک شفاهی | دقت کنترل | مهارت دستی | ترتیب‌دهی اطلاعات | اصالت | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | محیط سرپوشیده، کنترل‌شده از نظر دما | تاثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای تلفنی | برخورد با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | صرف زمان به صورت نشسته | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج کارگران دیگر</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | طراحان الگوهای پارچه و پوشاک | طراحان مد | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارکنان خشک‌شویی و لباس‌شویی | کارگران نشانه‌گذار خطوط برش فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگو سازان فلز و پلاستیک | الگو سازان چوب | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی منسوجات | رویه‌کوبان مبل</t>
+          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | الگوسازان پارچه و پوشاک | طراحان مد | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارکنان خشک‌شویی و لباس‌شویی | کارگران شابلون‌زنی، فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان صحافی و پرداخت چاپ | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | روکوبان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | دقت کنترل | بینایی نزدیک | تشخیص رنگ بصری | زبردستی دستی | کنترل سرعت | زبردستی انگشتان | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | تشخیص گفتار | بینایی دور | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | تجسم فضایی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مشکل | بیان شفاهی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | تشخیص رنگ بصری | مهارت دستی | کنترل نرخ | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | تشخیص گفتار | بینایی دور | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | محیط سرپوشیده، بدون کنترل دما | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورق‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ ذوب | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و همزن | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورهای چرخ خیاطی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سیم‌پیچی، تابندگی و کشش منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورهای چرخ خیاطی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0088_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0088_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت در کنترل | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | وضوح گفتار | تشخیص گفتار | هماهنگی اندام‌ها | چابکی انگشتان | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | سرعت ادراک | انعطاف‌پذیری بستن | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | تمایز رنگ بصری | دید دور | استحکام ایستا</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | مهارت انگشتان | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | تشخیص رنگ بصری | بینایی دور | قدرت ایستا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | قلم‌زنان و حکاکان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، قالب‌گیری، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به‌جز رایانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های چاپ عکس | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | حکاکان و اسیدکاران | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | مکانیک | خدمات مشتریان و خدمات فردی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی | چابکی دستی | ثبات دست و بازو | استدلال قیاسی | تجسم فضایی | وضوح گفتار | تشخیص گفتار | قدرت تنه | دقت در کنترل | توجه انتخابی | استدلال استقرایی | درک کتبی | هماهنگی اندام‌ها | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | مهارت انگشتان | حساسیت به مسئله | بیان شفاهی | درک شفاهی | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | تجسم | وضوح گفتار | تشخیص گفتار | قدرت تنه | دقت کنترل | توجه انتخابی | استدلال استقرایی | درک کتبی | هماهنگی چند عضو | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد وابسته | اپراتورهای ماشین‌های چاپ | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی و تریکوبافی نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تابندگی، دولاتابی و کشش الیاف نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد وابسته | اپراتورهای ماشین‌های چاپ | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | دقت در کنترل | چابکی دستی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | دقت کنترل | مهارت دستی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | پاک‌کنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات شستشو، پاک‌سازی و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برش‌کاران و پیراسته‌کاران دستی | ظرف‌شویان | پرداخت‌کاران مبلمان و مصنوعات چوبی | کارگران سنگ‌زنی و پرداخت دستی | کارگران کمکی تولید | سرایداران و نظافتچی‌ها، به‌جز خدمتکاران و نظافتچی‌های هتل و خانه | کارگران ساده جابجایی دستی بار و کالا | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و نظافتچی‌های هتل و اماکن | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و جعبه‌بندهای دستی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | اتوکاران منسوجات، پوشاک و مواد وابسته | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برشکاران و پیرایشگران دستی | ظرف‌شویان | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کمک‌کارگران خطوط تولید | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و نظافتچیان منازل و هتل‌ها | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | اتوکاران منسوجات، پوشاک و مواد وابسته | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار Microsoft Word | نرم‌افزار ایمیل</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دقت در کنترل | دید نزدیک | هماهنگی اندام‌ها | چابکی انگشتان | قدرت تنه | زمان واکنش</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | مهارت انگشتان | قدرت تنه | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، قالب‌گیری، پرس و فشرده‌سازی | کارگران سنگ‌زنی و پرداخت دستی | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و جعبه‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت در کنترل | دید نزدیک | چابکی انگشتان | کنترل نرخ حرکت | هماهنگی اندام‌ها | مرتب‌سازی اطلاعات | تمایز رنگ بصری | زمان واکنش | تجسم فضایی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | بینایی نزدیک | مهارت انگشتان | کنترل نرخ | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | زمان عکس‌العمل | تجسم | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی و تریکوبافی نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تابندگی، دولاتابی و کشش الیاف نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار حسابداری مالی | نرم‌افزار دفترداری | نرم‌افزار ردیابی موجودی | نرم‌افزار پردازش فروش | نرم‌افزار Microsoft Excel</t>
+          <t>نرم‌افزار حسابداری | نرم‌افزار دفترداری | نرم‌افزار ردیابی موجودی | نرم‌افزار پردازش فروش | نرم‌افزار Microsoft Excel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی انگشتان | حساسیت به مسئله | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت در کنترل | چابکی دستی | توجه انتخابی | تجسم فضایی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | مهارت دستی | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | قلم‌زنان و حکاکان | پرداخت‌کاران مبلمان و مصنوعات چوبی | کارگران سنگ‌زنی و پرداخت دستی | جواهرسازان و سازندگان مصنوعات فلزات و سنگ‌های قیمتی | تکنسین‌های ساخت پروتز و ارتزهای پزشکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | سنگ‌تراشان و حکاکان سنگ، بخش تولید | خیاطان و دوزندگان سفارشی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تایر‌سازان | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | حکاکان و اسیدکاران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | سنگ‌تراشان و حکاکان صنعتی سنگ | خیاطان و دوزندگان سفارشی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سازندگان تایر | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار کنترل تولید | نرم‌افزار ردیابی موجودی | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft PowerPoint | نرم‌افزار Microsoft Outlook</t>
+          <t>Adobe Acrobat | نرم‌افزار کنترل تولید | نرم‌افزار ردیابی موجودی | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft PowerPoint | Production control software</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری</t>
+          <t>تولید و فرآوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | دقت در کنترل | چابکی انگشتان | چابکی دستی | سرعت ادراک | حساسیت به مسئله | بیان شفاهی | زمان واکنش | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری دامنه حرکت</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | سرعت ادراکی | حساسیت به مسئله | بیان شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد وابسته | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تابندگی، دولاتابی و کشش الیاف نساجی | سنگ‌زنندگان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | اتوکاران منسوجات، پوشاک و مواد وابسته | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | دید نزدیک | دقت در کنترل | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | تمایز رنگ بصری | هماهنگی اندام‌ها</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران اسکلت، سطوح، مهارها و سیستم‌های هواپیما | برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | الگوسازان پارچه و پوشاک | پرداخت‌کاران مبلمان و مصنوعات چوبی | کارگران سنگ‌زنی و پرداخت دستی | جواهرسازان و سازندگان مصنوعات فلزات و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | سازندگان و نصابان سازه‌های فلزی | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی و تریکوبافی نساجی | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | الگوسازان پارچه و پوشاک | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | سازندگان و مونتاژکاران سازه‌های فلزی | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید و فرآوری | مدیریت و امور اداری | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | دید نزدیک | درک شفاهی | دقت در کنترل | چابکی دستی | مرتب‌سازی اطلاعات | ابتکار و اصالت | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>تجسم | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | درک شفاهی | دقت کنترل | مهارت دستی | ترتیب‌دهی اطلاعات | اصالت | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | الگوسازان پارچه و پوشاک | طراحان مد و لباس | جواهرسازان و سازندگان مصنوعات فلزات و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | نشانه‌گذاران و خط‌کشان قطعات فلزی و پلاستیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی و تریکوبافی نساجی | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | الگوسازان چوب | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران صحافی و تکمیل چاپ | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت در کنترل | دید نزدیک | تمایز رنگ بصری | چابکی دستی | کنترل نرخ حرکت | چابکی انگشتان | توجه انتخابی | سرعت ادراک | مرتب‌سازی اطلاعات | استدلال قیاسی | درک شفاهی | تشخیص گفتار | دید دور | قدرت تنه | استحکام ایستا | زمان واکنش | تجسم فضایی | انعطاف‌پذیری بستن | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | تشخیص رنگ بصری | مهارت دستی | کنترل نرخ | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | تشخیص گفتار | بینایی دور | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات شستشو، پاک‌سازی و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌شکن و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، قالب‌گیری، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌ها | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، تصفیه، ته‌نشینی و تقطیر | چرخکاران صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی و تریکوبافی نساجی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تابندگی، دولاتابی و کشش الیاف نساجی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | چرخکاران صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
